--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:16</t>
+    <t xml:space="preserve">2026-09-09 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:12</t>
+    <t xml:space="preserve">2026-09-17 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:08</t>
+    <t xml:space="preserve">2026-09-23 12:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:37</t>
+    <t xml:space="preserve">2026-10-02 14:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:28</t>
+    <t xml:space="preserve">2026-10-05 10:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
